--- a/Collections/Russia/#Russia#USSR#Commemorative#[1965-1991]#circulation_quality.xlsx
+++ b/Collections/Russia/#Russia#USSR#Commemorative#[1965-1991]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Russia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845AADA4-ECCF-43FC-BD61-511AEA9B272B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25759E7-E260-424B-91A8-FC837930E4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10копеек" sheetId="14" r:id="rId1"/>
@@ -41,6 +41,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2855,7 +2858,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 F3 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
+  <conditionalFormatting sqref="F3 F7 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
     <cfRule type="containsText" dxfId="89" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -2870,7 +2873,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
     <cfRule type="containsText" dxfId="88" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
@@ -3604,7 +3607,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 F3 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
+  <conditionalFormatting sqref="F3 F7 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
     <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -3619,7 +3622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
     <cfRule type="containsText" dxfId="85" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
@@ -4353,7 +4356,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 F3 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
+  <conditionalFormatting sqref="F3 F7 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
     <cfRule type="containsText" dxfId="83" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -4368,7 +4371,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
     <cfRule type="containsText" dxfId="82" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
@@ -5102,7 +5105,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7 F3 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
+  <conditionalFormatting sqref="F3 F7 F9 F11 F13 F15 F17 F19 F21 F23 F25 F27 F29">
     <cfRule type="containsText" dxfId="80" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -5117,7 +5120,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
     <cfRule type="containsText" dxfId="79" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
@@ -6850,12 +6853,12 @@
         <v>97</v>
       </c>
       <c r="F77" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="39"/>
       <c r="H77" s="13" t="str">
         <f t="shared" si="24"/>
-        <v/>
+        <v>Can exchange</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6882,6 +6885,16 @@
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="21">
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E46:E47"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
@@ -6893,18 +6906,8 @@
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E46:E47"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3 F18 F30 F57 F15 F23:F24 F38 F63 F6 F10 F44 F40 F68">
+  <conditionalFormatting sqref="F18 F3 F30 F57 F15 F23:F24 F38 F63 F6 F10 F44 F40 F68">
     <cfRule type="containsText" dxfId="78" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -6949,7 +6952,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F52 F32 F61">
+  <conditionalFormatting sqref="F52 F21 F32 F61">
     <cfRule type="containsText" dxfId="75" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -8426,7 +8429,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F27 F25 F29">
+  <conditionalFormatting sqref="F25 F27 F29">
     <cfRule type="containsText" dxfId="18" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
@@ -8441,7 +8444,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 F3 F7 F9 F11 F13 F15 F17 F19 F21 F23">
+  <conditionalFormatting sqref="F3 F5 F7 F9 F11 F13 F15 F17 F19 F21 F23">
     <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -8456,7 +8459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24 F26 F28">
     <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
@@ -9142,7 +9145,7 @@
         <v>96</v>
       </c>
       <c r="F33" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="39"/>
     </row>
@@ -9159,7 +9162,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="39"/>
     </row>
@@ -9220,7 +9223,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F25 F29 F32">
+  <conditionalFormatting sqref="F29 F25 F32">
     <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
@@ -9387,7 +9390,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 F3 F7 F9 F11 F13 F15 F17 F19 F21 F23">
+  <conditionalFormatting sqref="F3 F5 F7 F9 F11 F13 F15 F17 F19 F21 F23">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
@@ -9402,7 +9405,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 F4 F8 F10 F12 F14 F16 F18 F20 F22 F24">
+  <conditionalFormatting sqref="F4 F6 F8 F10 F12 F14 F16 F18 F20 F22 F24">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
